--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/08 14:59:13</t>
+          <t>09/16 21:57:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/02 13:48:56</t>
+          <t>09/08 14:59:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/01 15:45:01</t>
+          <t>09/02 13:48:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11695.91</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/01 10:16:07</t>
+          <t>09/01 15:45:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>11695.91</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/27 14:01:57</t>
+          <t>09/01 10:16:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21818.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/27 09:56:58</t>
+          <t>08/27 14:01:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>21818.18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/20 18:15:31</t>
+          <t>08/27 09:56:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08/20 18:15:31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>08/19 12:21:27</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>8333.33</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -538,7 +553,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -550,12 +565,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -565,7 +580,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -577,12 +592,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -604,12 +619,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -631,12 +646,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -658,12 +673,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -673,7 +688,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -685,12 +700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -700,7 +715,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -712,12 +727,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -727,7 +742,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -739,83 +754,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>710000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>85285.28</t>
+          <t>940000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>85284</t>
+          <t>112996.13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>85284</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1.28</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>27712.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/16 21:57:29</t>
+          <t>09/17 14:56:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>8139.53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/08 14:59:13</t>
+          <t>09/16 21:57:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/02 13:48:56</t>
+          <t>09/08 14:59:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/01 15:45:01</t>
+          <t>09/02 13:48:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11695.91</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/01 10:16:07</t>
+          <t>09/01 15:45:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>11695.91</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/27 14:01:57</t>
+          <t>09/01 10:16:07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21818.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/27 09:56:58</t>
+          <t>08/27 14:01:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>21818.18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/20 18:15:31</t>
+          <t>08/27 09:56:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>08/20 18:15:31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>08/19 12:21:27</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>8333.33</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -580,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -592,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -607,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -619,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -646,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -673,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -700,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -715,7 +730,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -727,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -742,7 +757,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -754,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -769,7 +784,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -781,83 +796,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>940000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>112996.13</t>
+          <t>1010000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>85284</t>
+          <t>121135.66</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>85284</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>27712.13</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>35851.66</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>09/17 16:38:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -796,12 +796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -823,83 +823,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1010000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>121135.66</t>
+          <t>1010000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>85284</t>
+          <t>121135.66</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>86284</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>35851.66</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>34851.66</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17 16:38:01</t>
+          <t>09/17 16:38:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>09/17 16:38:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +688,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +742,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -796,12 +796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -823,12 +823,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -850,83 +850,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1010000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>121135.66</t>
+          <t>1010000</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>86284</t>
+          <t>121135.66</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>93423</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>34851.66</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>27712.66</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 14:56:30</t>
+          <t>09/20 11:33:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/16 21:57:29</t>
+          <t>09/17 14:56:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>8139.53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/08 14:59:13</t>
+          <t>09/16 21:57:29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/02 13:48:56</t>
+          <t>09/08 14:59:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/01 15:45:01</t>
+          <t>09/02 13:48:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11695.91</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/01 10:16:07</t>
+          <t>09/01 15:45:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>11695.91</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/27 14:01:57</t>
+          <t>09/01 10:16:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21818.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/27 09:56:58</t>
+          <t>08/27 14:01:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>21818.18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/20 18:15:31</t>
+          <t>08/27 09:56:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>08/20 18:15:31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>08/19 12:21:27</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>8333.33</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17 16:38:54</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17 16:38:01</t>
+          <t>09/17 16:38:54</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>09/17 16:38:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +691,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -703,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -715,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -742,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -769,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -796,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -811,7 +826,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -823,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -838,7 +853,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -850,12 +865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -865,7 +880,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -877,83 +892,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1010000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>121135.66</t>
+          <t>1080000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93423</t>
+          <t>129275.2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>93423</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>27712.66</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>35852.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17 16:38:54</t>
+          <t>09/20 12:18:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -649,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17 16:38:01</t>
+          <t>09/17 16:38:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>09/17 16:38:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -784,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -865,12 +865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -892,12 +892,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -919,83 +919,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1080000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>129275.2</t>
+          <t>1080000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93423</t>
+          <t>129275.2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>94423</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>35852.2</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>34852.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -622,12 +622,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/20 12:18:03</t>
+          <t>09/20 12:45:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -649,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17 16:38:54</t>
+          <t>09/20 12:18:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17 16:38:01</t>
+          <t>09/17 16:38:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>09/17 16:38:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +730,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -757,12 +757,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +784,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +838,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,12 +865,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -892,12 +892,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -919,12 +919,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -946,83 +946,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1080000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>129275.2</t>
+          <t>1080000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>94423</t>
+          <t>129275.2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>101562</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>34852.2</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>27713.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 11:33:30</t>
+          <t>09/20 17:33:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8139.53</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17 14:56:30</t>
+          <t>09/20 11:33:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/16 21:57:29</t>
+          <t>09/17 14:56:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>8139.53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/08 14:59:13</t>
+          <t>09/16 21:57:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>27710.84</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/02 13:48:56</t>
+          <t>09/08 14:59:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/01 15:45:01</t>
+          <t>09/02 13:48:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11695.91</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/01 10:16:07</t>
+          <t>09/01 15:45:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>11695.91</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/27 14:01:57</t>
+          <t>09/01 10:16:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21818.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/27 09:56:58</t>
+          <t>08/27 14:01:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7142.86</t>
+          <t>21818.18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/20 18:15:31</t>
+          <t>08/27 09:56:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>7142.86</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>08/20 18:15:31</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5952.38</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>08/19 12:21:27</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>8333.33</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/20 12:45:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 12:18:03</t>
+          <t>09/20 12:45:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17 16:38:54</t>
+          <t>09/20 12:18:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -703,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17 16:38:01</t>
+          <t>09/17 16:38:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -730,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>09/17 16:38:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -757,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -772,7 +787,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -784,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -799,7 +814,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -811,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -838,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -865,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -892,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -907,7 +922,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -919,12 +934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -934,7 +949,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -946,12 +961,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -961,7 +976,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -973,83 +988,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1080000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>129275.2</t>
+          <t>1130000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>101562</t>
+          <t>135157.55</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>101562</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>27713.2</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>33595.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 12:45:32</t>
+          <t>09/20 17:33:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 12:18:03</t>
+          <t>09/20 12:45:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17 16:38:54</t>
+          <t>09/20 12:18:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17 16:38:01</t>
+          <t>09/17 16:38:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>09/17 16:38:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -826,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -880,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,12 +934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -961,12 +961,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -988,12 +988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1015,83 +1015,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>135157.55</t>
+          <t>1130000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>101562</t>
+          <t>135157.55</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>101850</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>33595.55</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>33307.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 17:33:26</t>
+          <t>09/20 18:37:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 12:45:32</t>
+          <t>09/20 17:33:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/20 12:18:03</t>
+          <t>09/20 12:45:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17 16:38:54</t>
+          <t>09/20 12:18:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17 16:38:01</t>
+          <t>09/17 16:38:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>09/17 16:38:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -826,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -880,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,12 +934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -961,12 +961,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -988,12 +988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1015,12 +1015,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1042,83 +1042,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>135157.55</t>
+          <t>1130000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>101850</t>
+          <t>135157.55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>102850</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>33307.55</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>32307.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-all.xlsx
@@ -664,12 +664,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 18:37:40</t>
+          <t>09/20 18:39:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 17:33:26</t>
+          <t>09/20 18:37:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -718,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/20 12:45:32</t>
+          <t>09/20 17:33:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/20 12:18:03</t>
+          <t>09/20 12:45:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17 16:38:54</t>
+          <t>09/20 12:18:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -799,12 +799,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17 16:38:01</t>
+          <t>09/17 16:38:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -826,12 +826,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
+          <t>09/17 16:38:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -853,12 +853,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>09/08 19:26:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -880,12 +880,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/02 15:02:41</t>
+          <t>09/08 14:59:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/01 17:26:18</t>
+          <t>09/02 15:02:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -934,12 +934,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/01 11:34:01</t>
+          <t>09/01 17:26:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -961,12 +961,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/27 15:15:22</t>
+          <t>09/01 11:34:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -988,12 +988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/27 10:05:01</t>
+          <t>08/27 15:15:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1015,12 +1015,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/20 19:49:17</t>
+          <t>08/27 10:05:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1042,12 +1042,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/20 18:15:36</t>
+          <t>08/20 19:49:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1069,83 +1069,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>08/20 18:15:36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>08/19 13:51:31</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>135157.55</t>
+          <t>1130000</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>102850</t>
+          <t>135157.55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>107445</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>32307.55</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>27712.55</t>
         </is>
       </c>
     </row>
